--- a/Boardline_Numbers.xlsx
+++ b/Boardline_Numbers.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -479,6 +479,8 @@
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -692,6 +694,16 @@
           <t>Phone 20 Number</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Phone 21 Label</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Phone 21 Number</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -778,22 +790,32 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>Enrollment (Alt)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>(855) 203-1384</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>Technical Support</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>(800) 925-3368</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>(855) 370-2406</t>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Alumni Relations</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>(877) 235-3561</t>
         </is>
       </c>
     </row>
@@ -980,6 +1002,96 @@
           <t>(888) 524-0093</t>
         </is>
       </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>Mobile, AL</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>(251) 288-6000</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>Montgomery, AL</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>(334) 523-3670</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>(904) 538-1000</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>Morrow, GA</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>(678) 422-4100</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>Suitland, MD</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>(301) 505-3300</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>North Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>(919) 301-6500</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>(610) 604-7700</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
+          <t>Nashville, TN</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="inlineStr">
+        <is>
+          <t>(615) 871-2260</t>
+        </is>
+      </c>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="AP5" s="2" t="inlineStr">
+        <is>
+          <t>(703) 892-5100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1192,6 +1304,16 @@
           <t>See website</t>
         </is>
       </c>
+      <c r="AQ6" s="2" t="inlineStr">
+        <is>
+          <t>Troy, MI</t>
+        </is>
+      </c>
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
+          <t>(248) 817-4140</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1372,6 +1494,26 @@
       <c r="AJ7" s="2" t="inlineStr">
         <is>
           <t>(972) 929-6777</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>Lisle, IL (HQ)</t>
+        </is>
+      </c>
+      <c r="AL7" s="2" t="inlineStr">
+        <is>
+          <t>(630) 428-9086</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>Gwinnett, GA</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="inlineStr">
+        <is>
+          <t>(770) 381-4400</t>
         </is>
       </c>
     </row>
